--- a/协作/29-变更记录.xlsx
+++ b/协作/29-变更记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -704,13 +704,127 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>变更-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>流程</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>v3.4：角色档位（单人/多人）+ 门禁可选启用 + 17/19/21/35/36 可选 + P0–P4 分阶段</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>v3.5：九角色全开 + 九门禁全开 + 37+3 全量必需 + 一次性全开不分阶段</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>用户明确要求零配置全开</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>旧项目升级需补缺交付物；本仓库已补 14 份并追加记录</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>用户+负责人</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>变更-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>交付物</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>模板与记录枚举</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18 类别仅 安全/性能/供应链；26 类型仅 表格/文档；28 状态仅 生效/已撤销；29 对象类型缺 流程/协议、状态缺 已生效；36 状态缺 已验收；37 当前状态缺 未发布</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>按实际记录取值扩枚举：18 增 兼容性/可运维性；26 增 记录/证据/模板/归档包；28 增 已生效；29 增 流程/协议 与 已生效；36 增 已验收；37 增 未发布</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>G0 要求枚举列取值必须在下拉内，原枚举写不进已有真实记录，属协议与模板不一致的真缺陷</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>§5.12/§5.18/§5.26/§5.28/§5.29/§5.36/§5.37；模板 6 份</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>架构契约+负责人</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"需求,契约,设计,路径,清单,交付物"</formula1>
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"需求,契约,设计,路径,清单,交付物,流程,协议"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"已完成,待批准"</formula1>
+    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"已完成,待批准,已生效"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/协作/29-变更记录.xlsx
+++ b/协作/29-变更记录.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -815,6 +815,58 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>证据-0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>变更-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>协议</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TEAMODEL v3.5（内置于 DCG）</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>协议 v3.5.1 外置于 https://github.com/CL98K/TEAMODEL.git（tag tm-v3.5.1）；DCG 移除 TEAMODEL.md、协作/模板/**、docs/TEAMODEL_draft_v1.md</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>协议要跨项目复用，且避免模板双真相</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DCG 版本库只剩自己写的交付物与记录；协议升版需更新 01 画像的引用版本号</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>架构契约+负责人</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>已生效</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
         </is>
       </c>
     </row>
